--- a/astro-site/public/dl/kit-tareas-dark-kitchen/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/03-tareas-manager.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Diario Manager'!$A$1:$G$29</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Semanal Manager'!$A$1:$G$29</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Mensual Manager'!$A$1:$G$27</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Handover Turno'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +82,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -140,44 +145,60 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -537,15 +558,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -553,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -560,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -574,6 +598,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -581,8 +606,33 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -596,16 +646,16 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist Diario del Manager / Operador</t>
@@ -619,10 +669,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -647,7 +698,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -664,10 +715,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -693,10 +742,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -722,10 +769,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -751,10 +796,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -780,10 +823,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -816,10 +857,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -845,10 +884,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -874,10 +911,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -903,10 +938,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -932,10 +965,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -961,10 +992,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -997,10 +1026,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1026,10 +1053,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1055,10 +1080,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1084,10 +1107,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="18" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
@@ -1113,10 +1134,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="19" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1141,6 +1160,7 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="C25" s="15" t="inlineStr">
         <is>
@@ -1149,14 +1169,19 @@
       </c>
       <c r="D25" s="16">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>de 16</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -1164,6 +1189,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -1181,7 +1207,17 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1196,16 +1232,16 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist Semanal (Lunes)</t>
@@ -1219,10 +1255,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1247,7 +1284,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1264,10 +1301,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1293,10 +1328,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1322,10 +1355,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1351,10 +1382,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1380,10 +1409,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1409,10 +1436,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1445,10 +1470,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1474,10 +1497,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1503,10 +1524,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1539,10 +1558,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1568,10 +1585,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1597,10 +1612,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1626,10 +1639,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1662,10 +1673,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="18" t="n">
+        <v>14</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
@@ -1691,10 +1700,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="19" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1719,6 +1726,7 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="C25" s="15" t="inlineStr">
         <is>
@@ -1727,14 +1735,19 @@
       </c>
       <c r="D25" s="16">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>de 15</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -1742,6 +1755,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -1756,11 +1770,21 @@
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F17 F18 F19 F20 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1775,16 +1799,16 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist Mensual</t>
@@ -1798,10 +1822,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1826,7 +1851,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1843,10 +1868,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1872,10 +1895,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1901,10 +1922,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1930,10 +1949,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1959,10 +1976,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1988,10 +2003,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -2024,10 +2037,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -2053,10 +2064,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -2082,10 +2091,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -2111,10 +2118,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -2147,10 +2152,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2176,10 +2179,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -2205,10 +2206,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -2234,10 +2233,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -2262,6 +2259,7 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="15" t="inlineStr">
         <is>
@@ -2270,14 +2268,19 @@
       </c>
       <c r="D23" s="16">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>de 14</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -2285,6 +2288,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
@@ -2302,7 +2306,17 @@
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -2317,16 +2331,16 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cambio de Turno</t>
@@ -2340,10 +2354,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2368,7 +2383,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2385,10 +2400,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2414,10 +2427,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -2443,10 +2454,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -2479,10 +2488,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -2508,10 +2515,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -2537,10 +2542,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -2573,10 +2576,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -2602,10 +2603,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -2631,10 +2630,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -2659,6 +2656,7 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="C18" s="15" t="inlineStr">
         <is>
@@ -2667,14 +2665,19 @@
       </c>
       <c r="D18" s="16">
         <f>COUNTIF(F5:F16,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>de 9</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -2682,6 +2685,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
@@ -2699,7 +2703,17 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/03-tareas-manager.xlsx
@@ -14,9 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -641,7 +645,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1217,8 +1221,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1227,7 +1239,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1784,8 +1796,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1794,7 +1814,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2316,8 +2336,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2326,7 +2354,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2713,7 +2741,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/03-tareas-manager.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +93,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +139,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -151,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +207,49 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,65 +627,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Tareas del Manager / Operador — Dark Kitchen</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Gestión de una dark kitchen multi-marca.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• KPIs clave: tiempo medio de preparación, rating por marca, tasa de cancelación</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• Delivery es el 100% del negocio — cada minuto cuenta</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>▸ Estás en 03-tareas-manager.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -647,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -697,7 +861,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -712,512 +876,604 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DE ACTIVAR</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Revisar previsión de pedidos (historial mismo día semana pasada)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Verificar equipo completo por turno</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Briefing: platos 86, promos activas en cada marca, incidencias</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Verificar stock crítico de todas las marcas</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Verificar que todas las tablets tienen batería y conexión</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE OPERACIÓN</t>
         </is>
       </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Monitorizar tiempos de preparación por marca</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Gestionar picos: redistribuir cocineros entre estaciones</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Resolver incidencias: pedidos incorrectos, riders que no llegan</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Pausar marcas si hay saturación (mejor pausar que hacer mal)</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Monitorizar ratings en tiempo real si hay quejas</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Gestionar reembolsos y contacto con soporte plataformas</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  AL CERRAR</t>
         </is>
       </c>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Desactivar todas las marcas</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Revisar facturación del día por plataforma y marca</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Anotar incidencias: cancelaciones, reembolsos, tiempos altos</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Hacer pedidos para mañana (proveedor principal + packaging)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Supervisar cierre de cocina</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cerrar y validar el registro diario de jornada del equipo (entradas, salidas y pausas)</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
     <row r="25">
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D25" s="16">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="32" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25">
-        <f>COUNTIF(B5:B23,"?*")</f>
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F31">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G23">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1241,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1263,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1547,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1306,493 +1562,591 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANÁLISIS</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Revisar ventas semana por marca y plataforma</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Analizar platos más vendidos por marca</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Revisar tiempo medio de preparación (objetivo &lt;12 min)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Analizar ratings por marca en cada plataforma</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Revisar tasa de cancelación y reembolsos</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Evaluar food cost por marca</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PEDIDOS</t>
         </is>
       </c>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Pedido semanal de ingredientes principales</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Pedido de packaging por marca (envases, bolsas, stickers)</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de productos de limpieza</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLATAFORMAS</t>
         </is>
       </c>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Actualizar fotos de platos si hay cambios</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Revisar que la ficha de cada plato declara sus alérgenos y que coincide con la receta REAL: si ha cambiado un ingrediente o un proveedor, ha cambiado el alérgeno</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Revisar precios vs competencia en cada plataforma</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Activar/desactivar promos según rendimiento</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Responder reseñas pendientes en todas las plataformas</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Supervisar limpieza profunda</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Verificar caducidades en almacén</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
     <row r="25">
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D25" s="16">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="32" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25">
-        <f>COUNTIF(B5:B23,"?*")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F31">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G23">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F17 F18 F19 F20 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F17 F18 F19 F20 F21 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1816,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1838,7 +2192,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1866,7 +2220,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1881,458 +2235,550 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  FINANCIERO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>P&amp;L por marca (ingresos - food cost - packaging - comisiones)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Food cost por marca (objetivo 25-30%)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Comisiones plataformas: Glovo ~30%, Uber Eats ~30%, Just Eat ~25%</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Coste de packaging por pedido</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Coste laboral vs facturación total</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes (hay que conservarlos 4 años)</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Evaluar rentabilidad de cada marca virtual</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARCAS</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Evaluar si alguna marca debe eliminarse (baja rentabilidad)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Evaluar lanzamiento de nueva marca virtual</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Rotar menús estacionales por marca</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Actualizar fotos profesionales de platos</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Revisión equipos: plancha, horno, freidora, cámaras</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Lavavajillas: filtros</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Campana: filtros</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Extintor y botiquín</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
     <row r="23">
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D23" s="16">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D29" s="16">
+        <f>COUNTIFS(B5:B27,"?*",F5:F27,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23">
-        <f>COUNTIF(B5:B21,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="F29">
+        <f>COUNTIF(B5:B27,"?*")-COUNTIF(F5:F27,"N/A")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A12:G12"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G21">
+  <conditionalFormatting sqref="A5:G27">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2356,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2406,7 +2852,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2421,323 +2867,388 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTADO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Pedidos en curso por marca</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Pedidos con incidencia (reclamación, retraso)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Marcas pausadas y motivo</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK</t>
         </is>
       </c>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Ingredientes que se están agotando</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Packaging que queda poco</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Estado del aceite de freidora</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Estado del aceite de la freidora y fecha del último cambio (el cambio se hace en frío, por debajo de 40 °C)</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  INCIDENCIAS</t>
         </is>
       </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Riders que no aparecieron</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Quejas de clientes recibidas</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Problemas técnicos: tablets, wifi, impresora</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
     <row r="18">
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D18" s="16">
-        <f>COUNTIF(F5:F16,"✓")</f>
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D23" s="16">
+        <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F18">
-        <f>COUNTIF(B5:B16,"?*")</f>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G16">
+  <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
